--- a/artfynd/A 35418-2026 artfynd.xlsx
+++ b/artfynd/A 35418-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193909</v>
       </c>
       <c r="B2" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136194146</v>
       </c>
       <c r="B3" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136194147</v>
       </c>
       <c r="B4" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136194148</v>
       </c>
       <c r="B5" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136194149</v>
       </c>
       <c r="B6" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136194150</v>
       </c>
       <c r="B7" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136194157</v>
       </c>
       <c r="B8" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35418-2026 artfynd.xlsx
+++ b/artfynd/A 35418-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193909</v>
       </c>
       <c r="B2" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136194146</v>
       </c>
       <c r="B3" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136194147</v>
       </c>
       <c r="B4" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136194148</v>
       </c>
       <c r="B5" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136194149</v>
       </c>
       <c r="B6" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136194150</v>
       </c>
       <c r="B7" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136194157</v>
       </c>
       <c r="B8" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35418-2026 artfynd.xlsx
+++ b/artfynd/A 35418-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193909</v>
       </c>
       <c r="B2" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136194146</v>
       </c>
       <c r="B3" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136194147</v>
       </c>
       <c r="B4" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136194148</v>
       </c>
       <c r="B5" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136194149</v>
       </c>
       <c r="B6" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136194150</v>
       </c>
       <c r="B7" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136194157</v>
       </c>
       <c r="B8" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35418-2026 artfynd.xlsx
+++ b/artfynd/A 35418-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193909</v>
       </c>
       <c r="B2" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136194146</v>
       </c>
       <c r="B3" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136194147</v>
       </c>
       <c r="B4" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136194148</v>
       </c>
       <c r="B5" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136194149</v>
       </c>
       <c r="B6" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136194150</v>
       </c>
       <c r="B7" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136194157</v>
       </c>
       <c r="B8" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35418-2026 artfynd.xlsx
+++ b/artfynd/A 35418-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193909</v>
       </c>
       <c r="B2" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136194146</v>
       </c>
       <c r="B3" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136194147</v>
       </c>
       <c r="B4" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136194148</v>
       </c>
       <c r="B5" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136194149</v>
       </c>
       <c r="B6" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136194150</v>
       </c>
       <c r="B7" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136194157</v>
       </c>
       <c r="B8" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35418-2026 artfynd.xlsx
+++ b/artfynd/A 35418-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193909</v>
       </c>
       <c r="B2" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136194146</v>
       </c>
       <c r="B3" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136194147</v>
       </c>
       <c r="B4" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136194148</v>
       </c>
       <c r="B5" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136194149</v>
       </c>
       <c r="B6" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136194150</v>
       </c>
       <c r="B7" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136194157</v>
       </c>
       <c r="B8" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35418-2026 artfynd.xlsx
+++ b/artfynd/A 35418-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193909</v>
       </c>
       <c r="B2" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136194146</v>
       </c>
       <c r="B3" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136194147</v>
       </c>
       <c r="B4" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136194148</v>
       </c>
       <c r="B5" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136194149</v>
       </c>
       <c r="B6" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136194150</v>
       </c>
       <c r="B7" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136194157</v>
       </c>
       <c r="B8" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35418-2026 artfynd.xlsx
+++ b/artfynd/A 35418-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193909</v>
       </c>
       <c r="B2" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136194146</v>
       </c>
       <c r="B3" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136194147</v>
       </c>
       <c r="B4" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136194148</v>
       </c>
       <c r="B5" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136194149</v>
       </c>
       <c r="B6" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136194150</v>
       </c>
       <c r="B7" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136194157</v>
       </c>
       <c r="B8" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35418-2026 artfynd.xlsx
+++ b/artfynd/A 35418-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,37 +680,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136193909</v>
+        <v>136481252</v>
       </c>
       <c r="B2" t="n">
-        <v>99341</v>
+        <v>93399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>810455</v>
+        <v>810364</v>
       </c>
       <c r="R2" t="n">
-        <v>7358259</v>
+        <v>7358281</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>06:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>06:53</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -795,13 +795,13 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136193909</t>
+          <t>https://artportalen.se/Sighting/136481252</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136194146</v>
+        <v>136193909</v>
       </c>
       <c r="B3" t="n">
         <v>99341</v>
@@ -840,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>810373</v>
+        <v>810455</v>
       </c>
       <c r="R3" t="n">
-        <v>7358401</v>
+        <v>7358259</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,12 +870,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -906,13 +916,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136194146</t>
+          <t>https://artportalen.se/Sighting/136193909</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136194147</v>
+        <v>136194146</v>
       </c>
       <c r="B4" t="n">
         <v>99341</v>
@@ -942,7 +952,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -951,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>810515</v>
+        <v>810373</v>
       </c>
       <c r="R4" t="n">
-        <v>7358368</v>
+        <v>7358401</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,12 +991,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1017,13 +1027,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136194147</t>
+          <t>https://artportalen.se/Sighting/136194146</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136194148</v>
+        <v>136194147</v>
       </c>
       <c r="B5" t="n">
         <v>99341</v>
@@ -1053,7 +1063,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>300</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1062,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>810534</v>
+        <v>810515</v>
       </c>
       <c r="R5" t="n">
-        <v>7358361</v>
+        <v>7358368</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,13 +1138,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136194148</t>
+          <t>https://artportalen.se/Sighting/136194147</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136194149</v>
+        <v>136194148</v>
       </c>
       <c r="B6" t="n">
         <v>99341</v>
@@ -1164,7 +1174,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1173,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>810561</v>
+        <v>810534</v>
       </c>
       <c r="R6" t="n">
-        <v>7358365</v>
+        <v>7358361</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,13 +1249,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136194149</t>
+          <t>https://artportalen.se/Sighting/136194148</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136194150</v>
+        <v>136194149</v>
       </c>
       <c r="B7" t="n">
         <v>99341</v>
@@ -1284,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>810516</v>
+        <v>810561</v>
       </c>
       <c r="R7" t="n">
-        <v>7358291</v>
+        <v>7358365</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,13 +1360,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136194150</t>
+          <t>https://artportalen.se/Sighting/136194149</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136194157</v>
+        <v>136194150</v>
       </c>
       <c r="B8" t="n">
         <v>99341</v>
@@ -1386,7 +1396,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1395,10 +1405,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>810421</v>
+        <v>810516</v>
       </c>
       <c r="R8" t="n">
-        <v>7358273</v>
+        <v>7358291</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,12 +1435,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1460,6 +1470,117 @@
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136194150</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136194157</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99341</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Norriån, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>810421</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7358273</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136194157</t>
         </is>
@@ -1474,6 +1595,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35418-2026 artfynd.xlsx
+++ b/artfynd/A 35418-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481252</v>
       </c>
       <c r="B2" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136193909</v>
       </c>
       <c r="B3" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136194146</v>
       </c>
       <c r="B4" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136194147</v>
       </c>
       <c r="B5" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136194148</v>
       </c>
       <c r="B6" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136194149</v>
       </c>
       <c r="B7" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>136194150</v>
       </c>
       <c r="B8" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>136194157</v>
       </c>
       <c r="B9" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
